--- a/src/test/resources/vacancycreation.xlsx
+++ b/src/test/resources/vacancycreation.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>Site Input</t>
   </si>
@@ -54,22 +54,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t xml:space="preserve"> apollo medical services</t>
-  </si>
-  <si>
-    <t>10012 - apollo medical services</t>
-  </si>
-  <si>
     <t>100010 - apollo</t>
   </si>
   <si>
-    <t>100011 - apollo</t>
-  </si>
-  <si>
     <t>December</t>
   </si>
   <si>
-    <t>January</t>
+    <t>1000123 - apollo</t>
   </si>
 </sst>
 </file>
@@ -441,16 +432,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>100011</v>
+        <v>1000123</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>2025</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -464,13 +455,13 @@
         <v>100010</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>2025</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -479,25 +470,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4">
-        <v>2025</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4">
-        <v>10</v>
-      </c>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -521,7 +500,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>100011</v>
+        <v>1000123</v>
       </c>
       <c r="B2">
         <v>22</v>
